--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250425120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1190,6 +1190,12 @@
   </si>
   <si>
     <t>Espace Santé Jeunes (ESJ)</t>
+  </si>
+  <si>
+    <t>704</t>
+  </si>
+  <si>
+    <t>Autre service territorial</t>
   </si>
   <si>
     <t/>
@@ -1484,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B186"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2960,15 +2966,23 @@
         <v>392</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>394</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -2995,7 +3009,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>41</v>
@@ -3003,42 +3017,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="407">
   <si>
     <t>Property</t>
   </si>
@@ -1136,6 +1136,12 @@
   </si>
   <si>
     <t>Structure qui contribue au Service d'Accès aux Soins</t>
+  </si>
+  <si>
+    <t>649</t>
+  </si>
+  <si>
+    <t>Centre de santé et de médiation en santé sexuelle</t>
   </si>
   <si>
     <t>695</t>
@@ -1490,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B186"/>
+  <dimension ref="A1:B187"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2974,15 +2980,23 @@
         <v>394</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>396</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -3009,7 +3023,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>41</v>
@@ -3017,42 +3031,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -433,7 +433,7 @@
     <t>231</t>
   </si>
   <si>
-    <t>Etablissement d'information, de consultation et de conseil familial</t>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
   </si>
   <si>
     <t>236</t>
@@ -997,7 +997,7 @@
     <t>617</t>
   </si>
   <si>
-    <t>Maison médicale de garde (MMG)</t>
+    <t>Lieu de soins non programmés</t>
   </si>
   <si>
     <t>618</t>
